--- a/data/gold-loan-providers.xlsx
+++ b/data/gold-loan-providers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GoldBazaar\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D76195-2343-4C18-8348-4177297873FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6967CAF-C728-4F40-A89C-AA799130350C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,7 +322,7 @@
     <t>₹30L</t>
   </si>
   <si>
-    <t>Muthoot Finance -Chandra</t>
+    <t>Muthoot Finance</t>
   </si>
 </sst>
 </file>

--- a/data/gold-loan-providers.xlsx
+++ b/data/gold-loan-providers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GoldBazaar\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6967CAF-C728-4F40-A89C-AA799130350C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35844F6-0CBD-41EC-8A39-63B2FA65E480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,7 +322,7 @@
     <t>₹30L</t>
   </si>
   <si>
-    <t>Muthoot Finance</t>
+    <t>Muthoot Finance - Chandra</t>
   </si>
 </sst>
 </file>

--- a/data/gold-loan-providers.xlsx
+++ b/data/gold-loan-providers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GoldBazaar\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35844F6-0CBD-41EC-8A39-63B2FA65E480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00F20EB-EA78-4E8C-B33D-B6F9E8133B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
   <si>
     <t>name</t>
   </si>
@@ -94,7 +94,10 @@
     <t>active</t>
   </si>
   <si>
-    <t>images/jeweler-logos/muthoot-finance.png</t>
+    <t>Kubera Treasury</t>
+  </si>
+  <si>
+    <t>images/logo.png</t>
   </si>
   <si>
     <t>NBFC · RBI Licensed</t>
@@ -127,7 +130,7 @@
     <t>RBI Licensed</t>
   </si>
   <si>
-    <t>https://www.muthootfinance.com</t>
+    <t>#</t>
   </si>
   <si>
     <t>Gold Power Plan</t>
@@ -154,10 +157,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Manappuram Finance</t>
-  </si>
-  <si>
-    <t>images/jeweler-logos/manappuram-finance.png</t>
+    <t>Vijayanagara Treasury</t>
   </si>
   <si>
     <t>South India · 3,000+ branches</t>
@@ -175,19 +175,16 @@
     <t>₹1 Crore</t>
   </si>
   <si>
-    <t>Gold ornaments (18K–24K) · Age 18–65 · No CIBIL check</t>
-  </si>
-  <si>
-    <t>Aadhaar / PAN · 1 photo · Gold jewellery</t>
-  </si>
-  <si>
-    <t>https://www.manappuram.com</t>
-  </si>
-  <si>
-    <t>Online Gold Loan</t>
-  </si>
-  <si>
-    <t>Apply digitally — no branch visit needed|Highest LTV at 80% — get more value from gold|Instant disbursal directly to bank account|No prepayment penalty — close loan anytime</t>
+    <t>Gold ornaments (18K–24K) · Age 18–65 · No CIBIL check required</t>
+  </si>
+  <si>
+    <t>Aadhaar / PAN · 1 passport photo · Gold jewellery</t>
+  </si>
+  <si>
+    <t>Digital Gold Loan</t>
+  </si>
+  <si>
+    <t>Apply digitally — no branch visit needed|Highest LTV at 80% — get more from your gold|Instant disbursal directly to bank account|No prepayment penalty — close loan anytime</t>
   </si>
   <si>
     <t>Bullet Repay</t>
@@ -199,10 +196,7 @@
     <t>₹1Cr</t>
   </si>
   <si>
-    <t>IIFL Finance</t>
-  </si>
-  <si>
-    <t>images/jeweler-logos/iifl-finance.png</t>
+    <t>Krishnadevaraya Vault</t>
   </si>
   <si>
     <t>Pan India · 1,000+ cities</t>
@@ -217,10 +211,7 @@
     <t>Gold jewellery 18K–22K · Age 18–70 · Salaried or self-employed</t>
   </si>
   <si>
-    <t>https://www.iifl.com/gold-loan</t>
-  </si>
-  <si>
-    <t>Home Loan Link</t>
+    <t>Smart OD Plan</t>
   </si>
   <si>
     <t>Lowest rate from 7.8% p.a. among NBFCs|Overdraft facility — draw only what you need|Pay interest only on the amount used|Renew online without returning gold to branch</t>
@@ -232,10 +223,7 @@
     <t>Overdraft account linked to gold — withdraw anytime|Interest charged only on amount withdrawn|Reuse repaid amount without fresh application|No foreclosure charges</t>
   </si>
   <si>
-    <t>IndusInd Bank</t>
-  </si>
-  <si>
-    <t>images/jeweler-logos/indusind-bank.png</t>
+    <t>Vikramaditya Reserve</t>
   </si>
   <si>
     <t>Scheduled Bank</t>
@@ -259,28 +247,22 @@
     <t>₹25 Lakh</t>
   </si>
   <si>
-    <t>Gold jewellery 18K–24K · Age 21–65 · Existing account preferred</t>
+    <t>Gold jewellery 18K–22K · Age 21–65 · Minimal documentation</t>
   </si>
   <si>
     <t>RBI Regulated</t>
   </si>
   <si>
-    <t>https://www.indusind.com</t>
-  </si>
-  <si>
-    <t>Indus Gold Loan</t>
-  </si>
-  <si>
-    <t>Bank-grade security — gold in insured RBI-grade vault|EMI flexibility — choose 12 to 36 month tenure|Competitive 8.2% rate — lower than most NBFCs|Track loan status via IndusInd mobile app</t>
+    <t>Gold Flex Plan</t>
+  </si>
+  <si>
+    <t>Flexible repayment — monthly or quarterly options|No penalty for early closure|Dedicated relationship manager assigned|Transparent fee structure — no hidden charges</t>
   </si>
   <si>
     <t>₹25L</t>
   </si>
   <si>
-    <t>Bajaj Finserv</t>
-  </si>
-  <si>
-    <t>images/jeweler-logos/bajaj-finserv.png</t>
+    <t>Chandragupta Capital</t>
   </si>
   <si>
     <t>NBFC · Listed Company</t>
@@ -304,32 +286,32 @@
     <t>₹30 Lakh</t>
   </si>
   <si>
-    <t>Gold ornaments 18K–22K · Age 21–70 · Any Indian citizen</t>
+    <t>Gold ornaments 18K–24K · Age 18–70 · Self-employed welcome</t>
   </si>
   <si>
     <t>SEBI Listed</t>
   </si>
   <si>
-    <t>https://www.bajajfinserv.in/gold-loan</t>
-  </si>
-  <si>
-    <t>Bajaj Flexi Loan</t>
-  </si>
-  <si>
-    <t>Prepay and re-draw as needed — full flexibility|500+ cities with 1,000+ partner centres|No part-payment charges — reduce interest anytime|Dedicated relationship manager for loans above ₹5L</t>
+    <t>Capital Shield</t>
+  </si>
+  <si>
+    <t>Lowest risk gold loan — fixed interest rate|Free secure vault storage during tenure|Complimentary insurance on pledged gold|Doorstep pickup in major cities</t>
+  </si>
+  <si>
+    <t>Growth Plus</t>
+  </si>
+  <si>
+    <t>Pay only interest during loan tenure|Principal repayment at maturity|Ideal for business owners and investors|No partial payment pressure</t>
   </si>
   <si>
     <t>₹30L</t>
-  </si>
-  <si>
-    <t>Muthoot Finance - Chandra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,17 +321,12 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFC9A84C"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,18 +335,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A1200"/>
-        <bgColor rgb="FF1A1200"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0E0B04"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF161000"/>
+        <fgColor rgb="FF2D2400"/>
       </patternFill>
     </fill>
   </fills>
@@ -385,17 +351,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,31 +659,10 @@
   <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="52" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
-    <col min="12" max="12" width="6" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="42" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="55" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="55" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="24" width="8" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,354 +736,356 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2">
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2">
         <v>5</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="N4" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" s="2" t="s">
+      <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="V4" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>43</v>
+      <c r="W4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X4" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>76</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>78</v>
+      </c>
+      <c r="U5" t="s">
+        <v>72</v>
+      </c>
+      <c r="V5" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="X5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="3">
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6">
         <v>4</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="2">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>91</v>
+      </c>
+      <c r="R6" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" t="s">
+        <v>93</v>
+      </c>
+      <c r="U6" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="V6" t="s">
         <v>94</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="2">
-        <v>4</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>43</v>
+      <c r="W6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
